--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ARKANSAS_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/ARKANSAS_2022.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C107">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C170">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C178">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C423">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C462">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C471">
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C498">
@@ -10381,7 +10381,7 @@
         <v>32</v>
       </c>
       <c r="D557">
-        <v>0.009016624401239785</v>
+        <v>0.009016624401239784</v>
       </c>
     </row>
     <row r="558">
@@ -10777,7 +10777,7 @@
         <v>32</v>
       </c>
       <c r="D579">
-        <v>0.009016624401239785</v>
+        <v>0.009016624401239784</v>
       </c>
     </row>
     <row r="580">
@@ -11119,7 +11119,7 @@
         <v>32</v>
       </c>
       <c r="D598">
-        <v>0.009016624401239785</v>
+        <v>0.009016624401239784</v>
       </c>
     </row>
     <row r="599">
